--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Provincia-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,82</t>
+          <t>-6,03; 5,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 6,94</t>
+          <t>-5,0; 6,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 10,11</t>
+          <t>-6,01; 10,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 1,77</t>
+          <t>-12,8; 1,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 6,09</t>
+          <t>-4,39; 5,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 2,18</t>
+          <t>-6,47; 2,47</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 50,25</t>
+          <t>-33,59; 48,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,56; 58,81</t>
+          <t>-29,06; 53,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 40,28</t>
+          <t>-17,05; 40,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 7,19</t>
+          <t>-36,93; 5,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 30,39</t>
+          <t>-18,4; 31,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 10,9</t>
+          <t>-25,98; 13,02</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 0,33</t>
+          <t>-9,37; 0,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 0,97</t>
+          <t>-8,82; 1,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 2,44</t>
+          <t>-8,62; 2,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 5,56</t>
+          <t>-4,63; 6,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 0,05</t>
+          <t>-7,8; -0,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 2,06</t>
+          <t>-5,62; 2,03</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,62; 1,62</t>
+          <t>-46,5; 0,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,41; 3,98</t>
+          <t>-42,45; 10,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 8,7</t>
+          <t>-26,45; 10,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 20,33</t>
+          <t>-13,73; 23,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 0,14</t>
+          <t>-29,84; -1,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 9,76</t>
+          <t>-21,23; 8,93</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -3,1</t>
+          <t>-14,61; -3,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,92</t>
+          <t>-3,74; 8,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 3,67</t>
+          <t>-9,78; 3,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 12,66</t>
+          <t>-0,28; 12,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,64; -1,78</t>
+          <t>-10,95; -1,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 9,46</t>
+          <t>-0,17; 9,09</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,1; -16,48</t>
+          <t>-60,78; -18,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 51,06</t>
+          <t>-15,93; 49,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 15,91</t>
+          <t>-33,85; 13,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 55,72</t>
+          <t>-1,08; 56,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-40,23; -7,72</t>
+          <t>-41,44; -8,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 46,25</t>
+          <t>-0,78; 42,98</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 7,26</t>
+          <t>-3,57; 7,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,26; 17,6</t>
+          <t>3,69; 17,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 6,43</t>
+          <t>-7,27; 6,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 4,3</t>
+          <t>-16,29; 3,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 4,94</t>
+          <t>-3,69; 5,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 8,4</t>
+          <t>-4,91; 8,12</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 62,23</t>
+          <t>-20,79; 57,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,31; 146,72</t>
+          <t>20,54; 135,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 22,81</t>
+          <t>-21,08; 21,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,69; 14,61</t>
+          <t>-45,63; 14,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 23,16</t>
+          <t>-14,65; 27,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 38,18</t>
+          <t>-20,32; 36,83</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 1,08</t>
+          <t>-14,54; 2,23</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,45; -1,03</t>
+          <t>-15,24; -1,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-26,09; -8,39</t>
+          <t>-27,18; -8,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-39,27; -15,75</t>
+          <t>-37,95; -15,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,69; -6,2</t>
+          <t>-18,13; -6,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,62; -10,32</t>
+          <t>-23,21; -9,83</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-56,4; 6,4</t>
+          <t>-55,85; 13,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,78; -4,91</t>
+          <t>-57,06; -8,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,93; -19,83</t>
+          <t>-52,48; -20,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-77,69; -36,67</t>
+          <t>-74,93; -35,49</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,27; -19,89</t>
+          <t>-48,71; -19,84</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,59; -32,91</t>
+          <t>-62,9; -31,76</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 3,02</t>
+          <t>-11,51; 2,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 8,09</t>
+          <t>-4,54; 8,89</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 1,13</t>
+          <t>-14,11; 1,26</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 10,95</t>
+          <t>-4,37; 10,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-11,17; -0,23</t>
+          <t>-10,54; 0,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,39</t>
+          <t>-2,79; 7,4</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,13; 15,24</t>
+          <t>-42,94; 13,42</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 40,92</t>
+          <t>-16,69; 47,18</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-40,72; 3,72</t>
+          <t>-37,67; 4,53</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 37,03</t>
+          <t>-11,51; 34,98</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,56; -0,85</t>
+          <t>-34,14; 1,72</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 28,71</t>
+          <t>-8,99; 29,73</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 2,46</t>
+          <t>-5,37; 2,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,45; 11,86</t>
+          <t>2,01; 11,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,16; -0,93</t>
+          <t>-11,34; -1,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 17,8</t>
+          <t>-12,49; 17,9</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,01; -0,69</t>
+          <t>-7,16; -0,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 12,67</t>
+          <t>-3,74; 12,95</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,45; 18,15</t>
+          <t>-30,66; 16,91</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13,2; 85,42</t>
+          <t>11,72; 83,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,93; -3,72</t>
+          <t>-36,88; -4,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 67,12</t>
+          <t>-43,34; 66,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,8; -3,33</t>
+          <t>-30,75; -2,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-18,21; 60,39</t>
+          <t>-16,22; 61,54</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 5,57</t>
+          <t>-1,88; 5,76</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-11,31; -0,15</t>
+          <t>-12,18; -0,32</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 4,84</t>
+          <t>-3,76; 4,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,1</t>
+          <t>-1,29; 6,66</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,16</t>
+          <t>-1,52; 4,36</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 1,72</t>
+          <t>-9,36; 1,8</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 44,43</t>
+          <t>-11,91; 46,32</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,03; -1,76</t>
+          <t>-72,17; -2,18</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 23,47</t>
+          <t>-14,57; 22,72</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 33,87</t>
+          <t>-5,23; 31,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 24,18</t>
+          <t>-7,56; 25,04</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-44,95; 9,11</t>
+          <t>-45,22; 10,05</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,75; -0,2</t>
+          <t>-3,79; -0,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,42</t>
+          <t>-3,43; 2,6</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,28</t>
+          <t>-5,43; -1,12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 3,53</t>
+          <t>-5,15; 3,41</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -1,38</t>
+          <t>-4,24; -1,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,48</t>
+          <t>-2,71; 2,51</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-20,93; -1,36</t>
+          <t>-21,14; -2,3</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 14,75</t>
+          <t>-19,55; 15,55</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-18,8; -4,53</t>
+          <t>-18,12; -3,97</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 12,49</t>
+          <t>-16,96; 12,05</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,43; -6,21</t>
+          <t>-17,58; -5,58</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 10,84</t>
+          <t>-11,77; 10,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_2-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>0,92</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-5,53</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,38</t>
+          <t>-2,22</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 5,95</t>
+          <t>-6,16; 5,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,34</t>
+          <t>-4,46; 6,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 10,2</t>
+          <t>-5,86; 10,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 1,36</t>
+          <t>-12,36; 0,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 5,96</t>
+          <t>-4,79; 5,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 2,47</t>
+          <t>-7,16; 1,85</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-17,82%</t>
+          <t>-18,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,74%</t>
+          <t>-10,02%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 48,07</t>
+          <t>-35,7; 50,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-29,06; 53,33</t>
+          <t>-24,63; 54,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 40,25</t>
+          <t>-17,32; 39,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 5,65</t>
+          <t>-35,42; 3,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,4; 31,25</t>
+          <t>-19,49; 28,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 13,02</t>
+          <t>-28,42; 9,94</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-3,96</t>
+          <t>-3,84</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-1,59</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 0,2</t>
+          <t>-10,64; 0,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 1,4</t>
+          <t>-8,84; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 2,93</t>
+          <t>-8,84; 2,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 6,36</t>
+          <t>-5,1; 5,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,8; -0,33</t>
+          <t>-7,91; -0,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 2,03</t>
+          <t>-5,11; 2,1</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-21,73%</t>
+          <t>-21,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-7,09%</t>
+          <t>-6,56%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 0,27</t>
+          <t>-48,3; 1,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 10,65</t>
+          <t>-40,87; 8,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,45; 10,75</t>
+          <t>-26,7; 7,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 23,75</t>
+          <t>-14,95; 20,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,84; -1,31</t>
+          <t>-30,69; -0,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 8,93</t>
+          <t>-19,64; 9,47</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,37</t>
+          <t>6,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,63</t>
+          <t>4,57</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,61; -3,28</t>
+          <t>-14,82; -2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 8,59</t>
+          <t>-3,81; 8,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 3,22</t>
+          <t>-10,51; 3,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 12,59</t>
+          <t>-0,0; 12,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -1,88</t>
+          <t>-10,6; -1,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 9,09</t>
+          <t>0,16; 9,05</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-60,78; -18,52</t>
+          <t>-59,92; -14,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 49,68</t>
+          <t>-16,03; 51,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 13,79</t>
+          <t>-34,42; 17,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 56,76</t>
+          <t>-0,41; 53,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,44; -8,47</t>
+          <t>-40,55; -6,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 42,98</t>
+          <t>0,64; 43,1</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10,47</t>
+          <t>8,96</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,41</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>5,67</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 7,03</t>
+          <t>-3,64; 7,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 17,01</t>
+          <t>2,22; 15,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 6,36</t>
+          <t>-7,02; 6,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 3,93</t>
+          <t>-4,17; 8,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,47</t>
+          <t>-4,16; 4,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 8,12</t>
+          <t>1,01; 10,07</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-13,89%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 57,67</t>
+          <t>-20,91; 57,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,54; 135,62</t>
+          <t>11,61; 121,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 21,47</t>
+          <t>-20,19; 21,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 14,0</t>
+          <t>-11,92; 30,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 27,07</t>
+          <t>-15,92; 23,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,32; 36,83</t>
+          <t>3,87; 47,82</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-8,31</t>
+          <t>-9,17</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-24,33</t>
+          <t>-20,39</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-15,69</t>
+          <t>-14,61</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 2,23</t>
+          <t>-15,5; 0,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -1,58</t>
+          <t>-17,3; -3,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,18; -8,82</t>
+          <t>-26,08; -8,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-37,95; -15,36</t>
+          <t>-27,87; -12,8</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,13; -6,21</t>
+          <t>-18,76; -6,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-23,21; -9,83</t>
+          <t>-19,96; -9,14</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-37,91%</t>
+          <t>-41,82%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-51,68%</t>
+          <t>-43,3%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-45,21%</t>
+          <t>-42,09%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 13,39</t>
+          <t>-55,23; 7,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-57,06; -8,39</t>
+          <t>-61,31; -13,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-52,48; -20,49</t>
+          <t>-51,64; -20,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,93; -35,49</t>
+          <t>-54,36; -30,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-48,71; -19,84</t>
+          <t>-48,83; -20,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,9; -31,76</t>
+          <t>-52,5; -28,73</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,34</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 2,43</t>
+          <t>-11,85; 2,5</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 8,89</t>
+          <t>-5,15; 8,28</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 1,26</t>
+          <t>-14,71; 1,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 10,62</t>
+          <t>-3,88; 10,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 0,3</t>
+          <t>-11,19; -0,27</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 7,4</t>
+          <t>-2,48; 6,9</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 13,42</t>
+          <t>-44,62; 12,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-16,69; 47,18</t>
+          <t>-18,56; 43,57</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 4,53</t>
+          <t>-39,11; 5,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 34,98</t>
+          <t>-9,95; 36,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 1,72</t>
+          <t>-36,1; -1,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 29,73</t>
+          <t>-7,99; 26,2</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>6,66</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5,82</t>
+          <t>16,12</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>11,63</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,22</t>
+          <t>-6,06; 2,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,52</t>
+          <t>2,6; 11,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,34; -1,07</t>
+          <t>-10,87; -1,57</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 17,9</t>
+          <t>11,04; 20,99</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-7,16; -0,52</t>
+          <t>-6,91; -0,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 12,95</t>
+          <t>8,54; 15,18</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>53,51%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,66; 16,91</t>
+          <t>-34,17; 18,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>11,72; 83,85</t>
+          <t>13,8; 80,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-36,88; -4,15</t>
+          <t>-36,6; -5,93</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-43,34; 66,91</t>
+          <t>37,8; 87,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-30,75; -2,54</t>
+          <t>-29,86; -3,49</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,22; 61,54</t>
+          <t>37,02; 79,1</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-4,68</t>
+          <t>-1,75</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2,72</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-0,01</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,76</t>
+          <t>-1,56; 6,09</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-12,18; -0,32</t>
+          <t>-5,06; 1,46</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 4,84</t>
+          <t>-3,51; 5,15</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 6,66</t>
+          <t>-2,37; 5,55</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,36</t>
+          <t>-1,87; 4,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 1,8</t>
+          <t>-2,46; 2,82</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-33,44%</t>
+          <t>-12,54%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-11,62%</t>
+          <t>-0,03%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 46,32</t>
+          <t>-10,77; 48,73</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-72,17; -2,18</t>
+          <t>-31,72; 12,26</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 22,72</t>
+          <t>-13,65; 24,94</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 31,59</t>
+          <t>-8,85; 25,97</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 25,04</t>
+          <t>-8,64; 23,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-45,22; 10,05</t>
+          <t>-12,16; 16,51</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>3,18</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,37</t>
+          <t>-3,84; -0,21</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 2,6</t>
+          <t>-0,77; 3,25</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -1,12</t>
+          <t>-5,73; -1,23</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 3,41</t>
+          <t>1,19; 5,39</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -1,26</t>
+          <t>-4,22; -1,42</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 2,51</t>
+          <t>0,81; 3,74</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-21,14; -2,3</t>
+          <t>-21,53; -1,19</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 15,55</t>
+          <t>-4,37; 20,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -3,97</t>
+          <t>-18,83; -4,3</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-16,96; 12,05</t>
+          <t>3,9; 19,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-17,58; -5,58</t>
+          <t>-17,68; -6,33</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 10,88</t>
+          <t>3,43; 16,74</t>
         </is>
       </c>
     </row>
